--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 22,39</t>
+          <t>-3,31; 22,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 24,24</t>
+          <t>-0,78; 24,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,38; 62,48</t>
+          <t>40,58; 61,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 8,4</t>
+          <t>-16,61; 7,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 16,25</t>
+          <t>-8,22; 15,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,53; 54,12</t>
+          <t>28,65; 53,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 11,67</t>
+          <t>-6,0; 10,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,35</t>
+          <t>-0,74; 16,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,79; 54,76</t>
+          <t>38,22; 54,63</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 119,02</t>
+          <t>-11,48; 124,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 124,5</t>
+          <t>-3,28; 132,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125,76; 348,51</t>
+          <t>129,0; 354,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 38,57</t>
+          <t>-47,86; 31,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 71,61</t>
+          <t>-24,48; 69,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,73; 252,16</t>
+          <t>75,34; 236,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 52,32</t>
+          <t>-20,67; 48,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 73,64</t>
+          <t>-3,57; 72,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,36; 246,66</t>
+          <t>122,45; 248,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 12,99</t>
+          <t>-14,96; 12,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 5,42</t>
+          <t>-20,18; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,64; 51,05</t>
+          <t>27,71; 50,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 0,31</t>
+          <t>-25,55; 0,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,71; -1,33</t>
+          <t>-24,7; -0,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,39; 50,37</t>
+          <t>27,18; 50,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 2,97</t>
+          <t>-16,82; 1,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -1,66</t>
+          <t>-18,79; -0,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 47,86</t>
+          <t>31,14; 47,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 43,09</t>
+          <t>-34,29; 39,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 19,55</t>
+          <t>-45,19; 19,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,5; 178,88</t>
+          <t>61,89; 174,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 1,64</t>
+          <t>-52,37; 1,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -3,58</t>
+          <t>-49,44; -0,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,22; 139,71</t>
+          <t>52,51; 146,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 8,94</t>
+          <t>-37,4; 5,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,58; -4,46</t>
+          <t>-40,17; -1,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,64; 140,59</t>
+          <t>68,28; 140,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 26,17</t>
+          <t>-0,56; 25,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 16,91</t>
+          <t>-10,0; 18,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,8; 72,21</t>
+          <t>45,58; 71,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 13,91</t>
+          <t>-9,71; 14,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 16,74</t>
+          <t>-7,0; 16,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,87; 63,05</t>
+          <t>35,62; 61,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 15,64</t>
+          <t>-1,83; 16,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 13,74</t>
+          <t>-4,96; 12,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45,11; 63,48</t>
+          <t>43,84; 62,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 145,56</t>
+          <t>-2,96; 142,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 90,48</t>
+          <t>-32,86; 101,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136,96; 424,65</t>
+          <t>130,89; 400,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 61,7</t>
+          <t>-29,03; 66,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 73,64</t>
+          <t>-21,04; 73,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>100,17; 291,6</t>
+          <t>105,0; 294,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 68,8</t>
+          <t>-5,73; 73,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 60,47</t>
+          <t>-16,2; 55,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>146,56; 295,95</t>
+          <t>136,07; 291,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 13,48</t>
+          <t>-4,64; 12,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 11,35</t>
+          <t>-5,84; 10,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,98; 55,03</t>
+          <t>36,37; 56,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 11,57</t>
+          <t>-5,64; 12,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 1,69</t>
+          <t>-14,5; 2,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,26; 46,97</t>
+          <t>29,62; 47,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 9,98</t>
+          <t>-2,64; 9,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 4,32</t>
+          <t>-8,31; 3,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,84; 49,36</t>
+          <t>36,33; 49,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 48,39</t>
+          <t>-12,16; 46,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 40,06</t>
+          <t>-16,1; 36,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,63; 197,29</t>
+          <t>93,78; 196,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 34,81</t>
+          <t>-13,66; 38,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,28; 5,02</t>
+          <t>-34,69; 8,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,07; 149,02</t>
+          <t>69,97; 150,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 31,41</t>
+          <t>-6,71; 29,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 13,17</t>
+          <t>-21,04; 12,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,82; 153,68</t>
+          <t>93,43; 155,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 7,15</t>
+          <t>-17,49; 6,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 13,32</t>
+          <t>-8,83; 13,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,72; 54,98</t>
+          <t>32,03; 53,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,26</t>
+          <t>-17,57; 6,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 9,97</t>
+          <t>-14,44; 10,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 32,65</t>
+          <t>6,38; 34,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 3,02</t>
+          <t>-14,19; 2,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 8,28</t>
+          <t>-8,8; 8,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,35; 38,8</t>
+          <t>19,43; 39,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 27,33</t>
+          <t>-42,41; 23,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 47,93</t>
+          <t>-22,31; 50,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74,18; 212,27</t>
+          <t>75,66; 196,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 16,74</t>
+          <t>-34,02; 17,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 25,71</t>
+          <t>-27,61; 26,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,9; 83,1</t>
+          <t>13,93; 90,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 8,33</t>
+          <t>-31,64; 6,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 22,69</t>
+          <t>-19,36; 22,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43,05; 109,81</t>
+          <t>44,78; 111,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 10,04</t>
+          <t>-17,04; 9,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 7,09</t>
+          <t>-20,63; 6,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,21; 43,12</t>
+          <t>15,76; 41,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 9,88</t>
+          <t>-16,51; 9,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 1,0</t>
+          <t>-24,74; 0,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,64; 56,83</t>
+          <t>29,87; 55,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 6,09</t>
+          <t>-13,83; 6,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,19; -0,5</t>
+          <t>-19,51; -1,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28,18; 45,36</t>
+          <t>27,8; 46,64</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 27,63</t>
+          <t>-36,58; 25,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 19,84</t>
+          <t>-42,57; 18,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32,31; 121,35</t>
+          <t>30,7; 117,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 29,76</t>
+          <t>-35,48; 30,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 3,89</t>
+          <t>-54,58; 2,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,47; 184,34</t>
+          <t>65,83; 174,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 16,5</t>
+          <t>-30,1; 17,48</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,08; -0,03</t>
+          <t>-42,87; -4,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60,44; 129,04</t>
+          <t>59,9; 130,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 7,64</t>
+          <t>-2,57; 7,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 6,16</t>
+          <t>-3,63; 6,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40,53; 50,37</t>
+          <t>39,8; 49,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,33</t>
+          <t>-7,46; 2,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 0,86</t>
+          <t>-9,04; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,03; 42,58</t>
+          <t>32,53; 42,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,55</t>
+          <t>-3,07; 3,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,72</t>
+          <t>-4,68; 1,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>38,02; 45,23</t>
+          <t>37,78; 45,0</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 25,19</t>
+          <t>-7,15; 25,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 20,21</t>
+          <t>-10,2; 20,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>113,45; 166,96</t>
+          <t>109,74; 167,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 6,72</t>
+          <t>-18,83; 6,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 2,44</t>
+          <t>-23,24; 0,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>80,42; 122,02</t>
+          <t>80,33; 122,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 10,57</t>
+          <t>-8,15; 11,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 5,14</t>
+          <t>-12,73; 5,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>102,38; 136,84</t>
+          <t>102,64; 136,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 22,48</t>
+          <t>-2,65; 23,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 24,14</t>
+          <t>-0,01; 25,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,58; 61,71</t>
+          <t>39,81; 61,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 7,36</t>
+          <t>-17,57; 7,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 15,42</t>
+          <t>-8,64; 16,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 53,56</t>
+          <t>28,15; 53,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 10,86</t>
+          <t>-5,64; 11,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 16,62</t>
+          <t>-0,71; 17,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,22; 54,63</t>
+          <t>38,85; 55,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 124,39</t>
+          <t>-9,95; 130,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 132,56</t>
+          <t>-2,17; 141,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129,0; 354,11</t>
+          <t>128,09; 345,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 31,69</t>
+          <t>-49,52; 30,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 69,76</t>
+          <t>-24,63; 65,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,34; 236,08</t>
+          <t>73,96; 236,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 48,96</t>
+          <t>-18,97; 50,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 72,28</t>
+          <t>-1,71; 76,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>122,45; 248,97</t>
+          <t>124,7; 264,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 12,19</t>
+          <t>-14,66; 11,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 6,02</t>
+          <t>-19,17; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,71; 50,49</t>
+          <t>26,5; 50,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 0,03</t>
+          <t>-27,25; -0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -0,37</t>
+          <t>-24,84; -1,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,18; 50,85</t>
+          <t>28,38; 51,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 1,86</t>
+          <t>-16,56; 2,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,79; -0,65</t>
+          <t>-18,31; -0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,14; 47,51</t>
+          <t>30,65; 47,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,29; 39,58</t>
+          <t>-34,15; 40,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 19,18</t>
+          <t>-43,75; 16,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,89; 174,57</t>
+          <t>58,68; 176,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 1,54</t>
+          <t>-55,18; -1,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,44; -0,64</t>
+          <t>-49,94; -5,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,51; 146,23</t>
+          <t>56,84; 146,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 5,28</t>
+          <t>-36,04; 6,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,17; -1,68</t>
+          <t>-40,71; -1,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,28; 140,67</t>
+          <t>64,86; 135,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 25,67</t>
+          <t>-2,31; 26,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 18,01</t>
+          <t>-9,93; 17,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,58; 71,09</t>
+          <t>48,0; 71,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 14,31</t>
+          <t>-9,2; 13,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 16,85</t>
+          <t>-8,06; 17,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,62; 61,81</t>
+          <t>37,2; 62,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 16,26</t>
+          <t>-1,26; 16,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 12,84</t>
+          <t>-6,41; 13,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,84; 62,61</t>
+          <t>44,3; 62,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 142,47</t>
+          <t>-7,31; 138,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 101,7</t>
+          <t>-33,57; 89,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130,89; 400,02</t>
+          <t>141,6; 416,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 66,65</t>
+          <t>-28,57; 62,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 73,98</t>
+          <t>-24,13; 72,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>105,0; 294,88</t>
+          <t>108,84; 285,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 73,3</t>
+          <t>-4,69; 71,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 55,65</t>
+          <t>-19,9; 59,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136,07; 291,38</t>
+          <t>146,07; 282,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 12,86</t>
+          <t>-4,4; 13,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 10,64</t>
+          <t>-6,24; 10,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,37; 56,22</t>
+          <t>36,58; 55,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 12,2</t>
+          <t>-5,14; 12,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 2,64</t>
+          <t>-14,65; 2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,62; 47,81</t>
+          <t>29,77; 48,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 9,55</t>
+          <t>-2,51; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 3,94</t>
+          <t>-8,26; 4,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,33; 49,42</t>
+          <t>36,2; 49,63</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 46,77</t>
+          <t>-12,47; 47,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 36,38</t>
+          <t>-16,77; 38,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,78; 196,1</t>
+          <t>97,06; 204,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 38,13</t>
+          <t>-12,98; 38,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 8,59</t>
+          <t>-36,37; 6,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,97; 150,14</t>
+          <t>69,26; 153,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 29,55</t>
+          <t>-6,69; 30,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 12,39</t>
+          <t>-21,17; 13,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,43; 155,77</t>
+          <t>93,68; 159,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 6,7</t>
+          <t>-16,87; 7,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 13,9</t>
+          <t>-9,67; 13,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,03; 53,68</t>
+          <t>32,24; 54,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 6,71</t>
+          <t>-16,96; 6,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 10,29</t>
+          <t>-12,85; 10,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,38; 34,08</t>
+          <t>6,19; 33,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 2,54</t>
+          <t>-15,28; 2,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 8,42</t>
+          <t>-8,64; 8,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,43; 39,11</t>
+          <t>19,85; 39,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 23,88</t>
+          <t>-41,65; 28,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 50,36</t>
+          <t>-23,42; 48,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75,66; 196,13</t>
+          <t>73,94; 201,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 17,46</t>
+          <t>-33,6; 16,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 26,72</t>
+          <t>-25,29; 27,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,93; 90,25</t>
+          <t>12,62; 86,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 6,93</t>
+          <t>-33,0; 5,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 22,89</t>
+          <t>-19,13; 24,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>44,78; 111,84</t>
+          <t>45,69; 113,13</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 9,1</t>
+          <t>-19,23; 10,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 6,98</t>
+          <t>-20,9; 6,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15,76; 41,2</t>
+          <t>14,85; 41,75</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 9,55</t>
+          <t>-16,95; 9,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 0,88</t>
+          <t>-26,5; -0,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,87; 55,19</t>
+          <t>31,57; 55,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 6,59</t>
+          <t>-12,97; 6,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,51; -1,37</t>
+          <t>-20,81; -0,54</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27,8; 46,64</t>
+          <t>26,89; 45,32</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 25,47</t>
+          <t>-37,97; 30,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 18,87</t>
+          <t>-43,96; 17,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30,7; 117,32</t>
+          <t>28,82; 118,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 30,42</t>
+          <t>-35,97; 29,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,58; 2,63</t>
+          <t>-57,49; -0,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65,83; 174,56</t>
+          <t>64,01; 170,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 17,48</t>
+          <t>-28,58; 18,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,87; -4,22</t>
+          <t>-44,9; -1,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59,9; 130,69</t>
+          <t>56,57; 127,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,57</t>
+          <t>-1,9; 7,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 6,29</t>
+          <t>-4,33; 5,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39,8; 49,81</t>
+          <t>40,23; 49,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,1</t>
+          <t>-7,04; 2,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,14</t>
+          <t>-8,48; 0,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,53; 42,65</t>
+          <t>32,88; 42,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,74</t>
+          <t>-3,14; 3,65</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,94</t>
+          <t>-4,96; 1,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>37,78; 45,0</t>
+          <t>37,92; 44,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 25,39</t>
+          <t>-5,49; 24,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 20,82</t>
+          <t>-12,22; 19,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>109,74; 167,04</t>
+          <t>110,7; 165,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 6,06</t>
+          <t>-17,89; 7,37</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 0,56</t>
+          <t>-21,53; 2,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>80,33; 122,25</t>
+          <t>83,48; 125,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 11,06</t>
+          <t>-8,51; 10,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 5,86</t>
+          <t>-13,28; 5,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>102,64; 136,13</t>
+          <t>102,55; 135,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45,58</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10,19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,62</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,54</t>
+          <t>51,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47,06</t>
+          <t>48,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 23,56</t>
+          <t>-15,03; 8,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 25,41</t>
+          <t>-9,13; 16,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,81; 61,3</t>
+          <t>34,81; 56,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 7,26</t>
+          <t>-4,08; 22,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 16,11</t>
+          <t>-1,81; 24,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,15; 53,82</t>
+          <t>39,64; 61,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 11,31</t>
+          <t>-6,0; 11,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 17,02</t>
+          <t>-1,26; 16,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,85; 55,0</t>
+          <t>41,11; 55,53</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-16,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>42,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>49,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>214,47%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-16,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>144,3%</t>
+          <t>211,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>176,51%</t>
+          <t>181,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 130,59</t>
+          <t>-44,63; 38,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 141,63</t>
+          <t>-26,16; 71,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128,09; 345,65</t>
+          <t>96,48; 267,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 30,46</t>
+          <t>-12,63; 119,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 65,51</t>
+          <t>-6,16; 124,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,96; 236,52</t>
+          <t>124,37; 346,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 50,48</t>
+          <t>-19,89; 52,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 76,41</t>
+          <t>-5,04; 73,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,7; 264,7</t>
+          <t>130,02; 252,41</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-13,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-12,82</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39,93</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,24</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,82</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,71</t>
+          <t>39,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 11,77</t>
+          <t>-27,24; 0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 4,94</t>
+          <t>-25,71; -1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 50,79</t>
+          <t>27,18; 50,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,25; -0,98</t>
+          <t>-13,27; 12,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -1,45</t>
+          <t>-19,35; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,38; 51,49</t>
+          <t>26,35; 51,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 2,25</t>
+          <t>-16,82; 2,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -0,69</t>
+          <t>-18,25; -1,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,65; 47,53</t>
+          <t>31,41; 47,7</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-30,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-29,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-2,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-19,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106,12%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-30,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-29,33%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>106,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 40,19</t>
+          <t>-53,21; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 16,55</t>
+          <t>-51,16; -3,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,68; 176,82</t>
+          <t>53,79; 140,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,18; -1,97</t>
+          <t>-31,47; 43,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -5,15</t>
+          <t>-43,98; 19,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,84; 146,21</t>
+          <t>58,62; 179,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 6,06</t>
+          <t>-36,88; 8,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,71; -1,86</t>
+          <t>-40,58; -4,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,86; 135,56</t>
+          <t>69,48; 140,53</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>12,59</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>60,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,25</t>
+          <t>61,62</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54,66</t>
+          <t>55,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 26,58</t>
+          <t>-9,8; 13,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 17,05</t>
+          <t>-7,95; 16,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,0; 71,68</t>
+          <t>35,38; 62,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 13,87</t>
+          <t>-1,22; 26,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 17,17</t>
+          <t>-10,73; 16,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,2; 62,06</t>
+          <t>49,27; 73,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,27</t>
+          <t>-2,18; 15,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 13,43</t>
+          <t>-4,89; 13,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44,3; 62,31</t>
+          <t>45,9; 64,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176,14%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>50,34%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>12,85%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>241,5%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,8%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>177,04%</t>
+          <t>246,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>202,46%</t>
+          <t>205,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 138,64</t>
+          <t>-30,21; 61,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 89,56</t>
+          <t>-24,71; 73,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141,6; 416,34</t>
+          <t>98,8; 291,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 62,05</t>
+          <t>-3,79; 145,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 72,56</t>
+          <t>-34,42; 90,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108,84; 285,52</t>
+          <t>141,48; 430,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 71,64</t>
+          <t>-7,05; 68,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 59,3</t>
+          <t>-16,82; 60,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>146,07; 282,72</t>
+          <t>148,12; 298,35</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40,53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45,66</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,52</t>
+          <t>44,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42,61</t>
+          <t>42,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 13,25</t>
+          <t>-6,21; 11,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 10,77</t>
+          <t>-15,45; 1,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 55,48</t>
+          <t>31,36; 48,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 12,53</t>
+          <t>-5,0; 13,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 2,28</t>
+          <t>-6,1; 11,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,77; 48,55</t>
+          <t>36,0; 52,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 9,98</t>
+          <t>-2,65; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 4,43</t>
+          <t>-7,83; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,2; 49,63</t>
+          <t>36,67; 48,5</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>108,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>12,69%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>137,76%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>106,15%</t>
+          <t>134,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>121,16%</t>
+          <t>121,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 47,14</t>
+          <t>-15,14; 34,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 38,13</t>
+          <t>-37,28; 5,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,06; 204,82</t>
+          <t>74,73; 152,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 38,57</t>
+          <t>-13,06; 48,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 6,74</t>
+          <t>-16,14; 40,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,26; 153,34</t>
+          <t>93,28; 192,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 30,57</t>
+          <t>-7,0; 31,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 13,69</t>
+          <t>-20,9; 13,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,68; 159,51</t>
+          <t>94,61; 153,73</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-5,66</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-5,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,75</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>43,87</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-5,66</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,97</t>
+          <t>43,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30,94</t>
+          <t>31,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 7,84</t>
+          <t>-18,16; 6,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 13,64</t>
+          <t>-14,29; 9,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,24; 54,36</t>
+          <t>7,05; 33,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 6,62</t>
+          <t>-17,62; 7,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 10,62</t>
+          <t>-10,39; 13,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 33,08</t>
+          <t>33,04; 55,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 2,0</t>
+          <t>-14,54; 3,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 8,69</t>
+          <t>-8,59; 8,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,85; 39,14</t>
+          <t>20,97; 39,7</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,48%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,13%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>48,26%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-15,14%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>126,28%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-12,48%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,13%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>126,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 28,2</t>
+          <t>-34,65; 16,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 48,91</t>
+          <t>-26,97; 25,71</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73,94; 201,9</t>
+          <t>13,93; 88,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 16,66</t>
+          <t>-41,02; 27,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 27,67</t>
+          <t>-24,97; 47,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,62; 86,55</t>
+          <t>73,76; 214,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 5,56</t>
+          <t>-32,19; 8,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 24,88</t>
+          <t>-19,41; 22,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>45,69; 113,13</t>
+          <t>48,05; 113,04</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-3,62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-13,13</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>45,94</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-4,27</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-6,97</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>29,53</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-13,13</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44,55</t>
+          <t>29,72</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37,16</t>
+          <t>37,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 10,61</t>
+          <t>-16,23; 9,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 6,17</t>
+          <t>-25,06; 1,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14,85; 41,75</t>
+          <t>32,98; 57,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 9,17</t>
+          <t>-18,62; 10,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -0,58</t>
+          <t>-20,52; 7,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,57; 55,7</t>
+          <t>16,01; 43,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 6,46</t>
+          <t>-13,39; 6,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -0,54</t>
+          <t>-19,19; -0,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26,89; 45,32</t>
+          <t>28,55; 45,84</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-9,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-32,61%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>114,1%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-10,04%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-16,42%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>69,54%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-9,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-32,61%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>110,63%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 30,3</t>
+          <t>-33,78; 29,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,96; 17,9</t>
+          <t>-55,17; 3,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28,82; 118,94</t>
+          <t>71,11; 189,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 29,7</t>
+          <t>-38,61; 27,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,49; -0,92</t>
+          <t>-41,57; 19,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,01; 170,06</t>
+          <t>33,05; 122,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 18,32</t>
+          <t>-29,15; 16,5</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,9; -1,59</t>
+          <t>-42,08; -0,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56,57; 127,28</t>
+          <t>60,72; 129,67</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-4,08</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39,36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>44,92</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,09</t>
+          <t>44,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>41,37</t>
+          <t>41,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,28</t>
+          <t>-7,17; 2,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,87</t>
+          <t>-8,62; 0,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40,23; 49,96</t>
+          <t>33,89; 44,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,63</t>
+          <t>-2,68; 7,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,72</t>
+          <t>-3,44; 6,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,88; 42,92</t>
+          <t>40,43; 49,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,65</t>
+          <t>-3,43; 3,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,94</t>
+          <t>-4,82; 1,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>37,92; 44,77</t>
+          <t>38,74; 45,25</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-5,91%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-10,93%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>105,5%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>3,74%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>136,33%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-5,91%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-10,93%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>102,09%</t>
+          <t>135,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>117,58%</t>
+          <t>119,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 24,07</t>
+          <t>-17,48; 6,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 19,29</t>
+          <t>-22,12; 2,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110,7; 165,98</t>
+          <t>84,59; 125,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 7,37</t>
+          <t>-7,85; 25,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 2,08</t>
+          <t>-9,89; 20,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>83,48; 125,04</t>
+          <t>112,21; 163,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 10,75</t>
+          <t>-9,22; 10,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 5,9</t>
+          <t>-13,12; 5,14</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>102,55; 135,56</t>
+          <t>104,06; 136,96</t>
         </is>
       </c>
     </row>
